--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125830876</v>
+        <v>125830901</v>
       </c>
       <c r="B7" t="n">
-        <v>57811</v>
+        <v>92502</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754171</v>
+        <v>754244</v>
       </c>
       <c r="R7" t="n">
-        <v>7232818</v>
+        <v>7232864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125830901</v>
+        <v>125830876</v>
       </c>
       <c r="B8" t="n">
-        <v>92502</v>
+        <v>57811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754244</v>
+        <v>754171</v>
       </c>
       <c r="R8" t="n">
-        <v>7232864</v>
+        <v>7232818</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125830879</v>
+        <v>125830898</v>
       </c>
       <c r="B25" t="n">
-        <v>97208</v>
+        <v>92502</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754396</v>
+        <v>754233</v>
       </c>
       <c r="R25" t="n">
-        <v>7232865</v>
+        <v>7232850</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,32 +3017,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125830898</v>
+        <v>125830893</v>
       </c>
       <c r="B26" t="n">
-        <v>92502</v>
+        <v>78967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>754233</v>
+        <v>754361</v>
       </c>
       <c r="R26" t="n">
-        <v>7232850</v>
+        <v>7232867</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,32 +3114,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125830893</v>
+        <v>125830879</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>97208</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>754361</v>
+        <v>754396</v>
       </c>
       <c r="R27" t="n">
-        <v>7232867</v>
+        <v>7232865</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830883</v>
       </c>
       <c r="B2" t="n">
-        <v>91216</v>
+        <v>91223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125830880</v>
+        <v>125830903</v>
       </c>
       <c r="B3" t="n">
-        <v>97208</v>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754257</v>
+        <v>754728</v>
       </c>
       <c r="R3" t="n">
-        <v>7232865</v>
+        <v>7232863</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125830903</v>
+        <v>125830880</v>
       </c>
       <c r="B4" t="n">
-        <v>92502</v>
+        <v>97215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754728</v>
+        <v>754257</v>
       </c>
       <c r="R4" t="n">
-        <v>7232863</v>
+        <v>7232865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125830901</v>
+        <v>125830876</v>
       </c>
       <c r="B7" t="n">
-        <v>92502</v>
+        <v>57811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754244</v>
+        <v>754171</v>
       </c>
       <c r="R7" t="n">
-        <v>7232864</v>
+        <v>7232818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125830876</v>
+        <v>125830901</v>
       </c>
       <c r="B8" t="n">
-        <v>57811</v>
+        <v>92509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754171</v>
+        <v>754244</v>
       </c>
       <c r="R8" t="n">
-        <v>7232818</v>
+        <v>7232864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>125830899</v>
       </c>
       <c r="B10" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125830902</v>
+        <v>125830906</v>
       </c>
       <c r="B12" t="n">
-        <v>92502</v>
+        <v>78373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>754793</v>
+        <v>754373</v>
       </c>
       <c r="R12" t="n">
-        <v>7232966</v>
+        <v>7232867</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125830906</v>
+        <v>125830902</v>
       </c>
       <c r="B13" t="n">
-        <v>78373</v>
+        <v>92509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>754373</v>
+        <v>754793</v>
       </c>
       <c r="R13" t="n">
-        <v>7232867</v>
+        <v>7232966</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125830874</v>
+        <v>125830900</v>
       </c>
       <c r="B14" t="n">
-        <v>56843</v>
+        <v>92509</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>754163</v>
+        <v>754156</v>
       </c>
       <c r="R14" t="n">
-        <v>7232894</v>
+        <v>7232842</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1910,11 +1910,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125830900</v>
+        <v>125830874</v>
       </c>
       <c r="B15" t="n">
-        <v>92502</v>
+        <v>56843</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754156</v>
+        <v>754163</v>
       </c>
       <c r="R15" t="n">
-        <v>7232842</v>
+        <v>7232894</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2012,6 +2007,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2135,45 +2135,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125830895</v>
+        <v>125830875</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754569</v>
+        <v>754186</v>
       </c>
       <c r="R17" t="n">
-        <v>7232779</v>
+        <v>7232895</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2206,6 +2210,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,49 +2241,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125830875</v>
+        <v>125830895</v>
       </c>
       <c r="B18" t="n">
-        <v>56843</v>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754186</v>
+        <v>754569</v>
       </c>
       <c r="R18" t="n">
-        <v>7232895</v>
+        <v>7232779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2307,11 +2312,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2338,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125830881</v>
+        <v>125830888</v>
       </c>
       <c r="B19" t="n">
-        <v>92700</v>
+        <v>78967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754471</v>
+        <v>754263</v>
       </c>
       <c r="R19" t="n">
-        <v>7232852</v>
+        <v>7232863</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2435,7 +2435,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125830888</v>
+        <v>125830889</v>
       </c>
       <c r="B20" t="n">
         <v>78967</v>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754263</v>
+        <v>754295</v>
       </c>
       <c r="R20" t="n">
-        <v>7232863</v>
+        <v>7232868</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125830889</v>
+        <v>125830896</v>
       </c>
       <c r="B21" t="n">
         <v>78967</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754295</v>
+        <v>754778</v>
       </c>
       <c r="R21" t="n">
-        <v>7232868</v>
+        <v>7232929</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125830896</v>
+        <v>125830881</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>92707</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754778</v>
+        <v>754471</v>
       </c>
       <c r="R22" t="n">
-        <v>7232929</v>
+        <v>7232852</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2923,7 +2923,7 @@
         <v>125830898</v>
       </c>
       <c r="B25" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>125830879</v>
       </c>
       <c r="B27" t="n">
-        <v>97208</v>
+        <v>97215</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>125830878</v>
       </c>
       <c r="B28" t="n">
-        <v>97208</v>
+        <v>97215</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125830876</v>
+        <v>125830901</v>
       </c>
       <c r="B7" t="n">
-        <v>57811</v>
+        <v>92509</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754171</v>
+        <v>754244</v>
       </c>
       <c r="R7" t="n">
-        <v>7232818</v>
+        <v>7232864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125830901</v>
+        <v>125830876</v>
       </c>
       <c r="B8" t="n">
-        <v>92509</v>
+        <v>57811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754244</v>
+        <v>754171</v>
       </c>
       <c r="R8" t="n">
-        <v>7232864</v>
+        <v>7232818</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125830906</v>
+        <v>125830902</v>
       </c>
       <c r="B12" t="n">
-        <v>78373</v>
+        <v>92509</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>754373</v>
+        <v>754793</v>
       </c>
       <c r="R12" t="n">
-        <v>7232867</v>
+        <v>7232966</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125830902</v>
+        <v>125830906</v>
       </c>
       <c r="B13" t="n">
-        <v>92509</v>
+        <v>78373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>754793</v>
+        <v>754373</v>
       </c>
       <c r="R13" t="n">
-        <v>7232966</v>
+        <v>7232867</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125830874</v>
+        <v>125830894</v>
       </c>
       <c r="B15" t="n">
-        <v>56843</v>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754163</v>
+        <v>754346</v>
       </c>
       <c r="R15" t="n">
-        <v>7232894</v>
+        <v>7232860</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2007,11 +2007,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2038,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125830894</v>
+        <v>125830874</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754346</v>
+        <v>754163</v>
       </c>
       <c r="R16" t="n">
-        <v>7232860</v>
+        <v>7232894</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2109,6 +2104,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125830888</v>
+        <v>125830881</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>92707</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754263</v>
+        <v>754471</v>
       </c>
       <c r="R19" t="n">
-        <v>7232863</v>
+        <v>7232852</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2435,7 +2435,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125830889</v>
+        <v>125830888</v>
       </c>
       <c r="B20" t="n">
         <v>78967</v>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754295</v>
+        <v>754263</v>
       </c>
       <c r="R20" t="n">
-        <v>7232868</v>
+        <v>7232863</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125830896</v>
+        <v>125830889</v>
       </c>
       <c r="B21" t="n">
         <v>78967</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754778</v>
+        <v>754295</v>
       </c>
       <c r="R21" t="n">
-        <v>7232929</v>
+        <v>7232868</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125830881</v>
+        <v>125830896</v>
       </c>
       <c r="B22" t="n">
-        <v>92707</v>
+        <v>78967</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754471</v>
+        <v>754778</v>
       </c>
       <c r="R22" t="n">
-        <v>7232852</v>
+        <v>7232929</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830883</v>
       </c>
       <c r="B2" t="n">
-        <v>91223</v>
+        <v>91224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125830903</v>
       </c>
       <c r="B3" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125830880</v>
       </c>
       <c r="B4" t="n">
-        <v>97215</v>
+        <v>97216</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125830891</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125830901</v>
       </c>
       <c r="B7" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125830904</v>
       </c>
       <c r="B9" t="n">
-        <v>77916</v>
+        <v>77917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125830899</v>
+        <v>125830887</v>
       </c>
       <c r="B10" t="n">
-        <v>92509</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>754209</v>
+        <v>754137</v>
       </c>
       <c r="R10" t="n">
-        <v>7232812</v>
+        <v>7232854</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125830887</v>
+        <v>125830899</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>92510</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>754137</v>
+        <v>754209</v>
       </c>
       <c r="R11" t="n">
-        <v>7232854</v>
+        <v>7232812</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>125830902</v>
       </c>
       <c r="B12" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125830906</v>
       </c>
       <c r="B13" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125830900</v>
+        <v>125830894</v>
       </c>
       <c r="B14" t="n">
-        <v>92509</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>754156</v>
+        <v>754346</v>
       </c>
       <c r="R14" t="n">
-        <v>7232842</v>
+        <v>7232860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125830894</v>
+        <v>125830900</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>92510</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754346</v>
+        <v>754156</v>
       </c>
       <c r="R15" t="n">
-        <v>7232860</v>
+        <v>7232842</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,49 +2135,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125830875</v>
+        <v>125830895</v>
       </c>
       <c r="B17" t="n">
-        <v>56843</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754186</v>
+        <v>754569</v>
       </c>
       <c r="R17" t="n">
-        <v>7232895</v>
+        <v>7232779</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,11 +2206,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2241,45 +2232,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125830895</v>
+        <v>125830875</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754569</v>
+        <v>754186</v>
       </c>
       <c r="R18" t="n">
-        <v>7232779</v>
+        <v>7232895</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2312,6 +2307,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2338,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125830881</v>
+        <v>125830888</v>
       </c>
       <c r="B19" t="n">
-        <v>92707</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754471</v>
+        <v>754263</v>
       </c>
       <c r="R19" t="n">
-        <v>7232852</v>
+        <v>7232863</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125830888</v>
+        <v>125830889</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754263</v>
+        <v>754295</v>
       </c>
       <c r="R20" t="n">
-        <v>7232863</v>
+        <v>7232868</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125830889</v>
+        <v>125830896</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754295</v>
+        <v>754778</v>
       </c>
       <c r="R21" t="n">
-        <v>7232868</v>
+        <v>7232929</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125830896</v>
+        <v>125830881</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>92708</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754778</v>
+        <v>754471</v>
       </c>
       <c r="R22" t="n">
-        <v>7232929</v>
+        <v>7232852</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,7 +2729,7 @@
         <v>125830892</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>125830890</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>125830898</v>
       </c>
       <c r="B25" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>125830893</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>125830879</v>
       </c>
       <c r="B27" t="n">
-        <v>97215</v>
+        <v>97216</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>125830878</v>
       </c>
       <c r="B28" t="n">
-        <v>97215</v>
+        <v>97216</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>125830873</v>
       </c>
       <c r="B29" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125830903</v>
       </c>
       <c r="B3" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125830880</v>
       </c>
       <c r="B4" t="n">
-        <v>97216</v>
+        <v>97218</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125830901</v>
+        <v>125830876</v>
       </c>
       <c r="B7" t="n">
-        <v>92510</v>
+        <v>57811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754244</v>
+        <v>754171</v>
       </c>
       <c r="R7" t="n">
-        <v>7232864</v>
+        <v>7232818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125830876</v>
+        <v>125830901</v>
       </c>
       <c r="B8" t="n">
-        <v>57811</v>
+        <v>92518</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754171</v>
+        <v>754244</v>
       </c>
       <c r="R8" t="n">
-        <v>7232818</v>
+        <v>7232864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>125830899</v>
       </c>
       <c r="B11" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125830902</v>
+        <v>125830906</v>
       </c>
       <c r="B12" t="n">
-        <v>92510</v>
+        <v>78374</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>754793</v>
+        <v>754373</v>
       </c>
       <c r="R12" t="n">
-        <v>7232966</v>
+        <v>7232867</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125830906</v>
+        <v>125830902</v>
       </c>
       <c r="B13" t="n">
-        <v>78374</v>
+        <v>92518</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>754373</v>
+        <v>754793</v>
       </c>
       <c r="R13" t="n">
-        <v>7232867</v>
+        <v>7232966</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,7 +1939,7 @@
         <v>125830900</v>
       </c>
       <c r="B15" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2135,45 +2135,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125830895</v>
+        <v>125830875</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>56843</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754569</v>
+        <v>754186</v>
       </c>
       <c r="R17" t="n">
-        <v>7232779</v>
+        <v>7232895</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2206,6 +2210,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,49 +2241,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125830875</v>
+        <v>125830895</v>
       </c>
       <c r="B18" t="n">
-        <v>56843</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754186</v>
+        <v>754569</v>
       </c>
       <c r="R18" t="n">
-        <v>7232895</v>
+        <v>7232779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2307,11 +2312,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,7 +2632,7 @@
         <v>125830881</v>
       </c>
       <c r="B22" t="n">
-        <v>92708</v>
+        <v>92710</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125830898</v>
+        <v>125830879</v>
       </c>
       <c r="B25" t="n">
-        <v>92510</v>
+        <v>97218</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754233</v>
+        <v>754396</v>
       </c>
       <c r="R25" t="n">
-        <v>7232850</v>
+        <v>7232865</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,32 +3017,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125830893</v>
+        <v>125830898</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>92518</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>754361</v>
+        <v>754233</v>
       </c>
       <c r="R26" t="n">
-        <v>7232867</v>
+        <v>7232850</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,32 +3114,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125830879</v>
+        <v>125830893</v>
       </c>
       <c r="B27" t="n">
-        <v>97216</v>
+        <v>78968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>754396</v>
+        <v>754361</v>
       </c>
       <c r="R27" t="n">
-        <v>7232865</v>
+        <v>7232867</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,7 +3214,7 @@
         <v>125830878</v>
       </c>
       <c r="B28" t="n">
-        <v>97216</v>
+        <v>97218</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125830906</v>
+        <v>125830902</v>
       </c>
       <c r="B12" t="n">
-        <v>78374</v>
+        <v>92518</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>754373</v>
+        <v>754793</v>
       </c>
       <c r="R12" t="n">
-        <v>7232867</v>
+        <v>7232966</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125830902</v>
+        <v>125830906</v>
       </c>
       <c r="B13" t="n">
-        <v>92518</v>
+        <v>78374</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>754793</v>
+        <v>754373</v>
       </c>
       <c r="R13" t="n">
-        <v>7232966</v>
+        <v>7232867</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2135,49 +2135,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125830875</v>
+        <v>125830895</v>
       </c>
       <c r="B17" t="n">
-        <v>56843</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754186</v>
+        <v>754569</v>
       </c>
       <c r="R17" t="n">
-        <v>7232895</v>
+        <v>7232779</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,11 +2206,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2241,45 +2232,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125830895</v>
+        <v>125830875</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>56843</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754569</v>
+        <v>754186</v>
       </c>
       <c r="R18" t="n">
-        <v>7232779</v>
+        <v>7232895</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2312,6 +2307,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2338,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125830888</v>
+        <v>125830881</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>92710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754263</v>
+        <v>754471</v>
       </c>
       <c r="R19" t="n">
-        <v>7232863</v>
+        <v>7232852</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2435,7 +2435,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125830889</v>
+        <v>125830888</v>
       </c>
       <c r="B20" t="n">
         <v>78968</v>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754295</v>
+        <v>754263</v>
       </c>
       <c r="R20" t="n">
-        <v>7232868</v>
+        <v>7232863</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125830896</v>
+        <v>125830889</v>
       </c>
       <c r="B21" t="n">
         <v>78968</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754778</v>
+        <v>754295</v>
       </c>
       <c r="R21" t="n">
-        <v>7232929</v>
+        <v>7232868</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125830881</v>
+        <v>125830896</v>
       </c>
       <c r="B22" t="n">
-        <v>92710</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754471</v>
+        <v>754778</v>
       </c>
       <c r="R22" t="n">
-        <v>7232852</v>
+        <v>7232929</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830883</v>
       </c>
       <c r="B2" t="n">
-        <v>91224</v>
+        <v>91228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125830903</v>
+        <v>125830880</v>
       </c>
       <c r="B3" t="n">
-        <v>92518</v>
+        <v>97222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754728</v>
+        <v>754257</v>
       </c>
       <c r="R3" t="n">
-        <v>7232863</v>
+        <v>7232865</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125830880</v>
+        <v>125830903</v>
       </c>
       <c r="B4" t="n">
-        <v>97218</v>
+        <v>92522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754257</v>
+        <v>754728</v>
       </c>
       <c r="R4" t="n">
-        <v>7232865</v>
+        <v>7232863</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>125830891</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125830876</v>
+        <v>125830901</v>
       </c>
       <c r="B7" t="n">
-        <v>57811</v>
+        <v>92522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754171</v>
+        <v>754244</v>
       </c>
       <c r="R7" t="n">
-        <v>7232818</v>
+        <v>7232864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125830901</v>
+        <v>125830876</v>
       </c>
       <c r="B8" t="n">
-        <v>92518</v>
+        <v>57811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754244</v>
+        <v>754171</v>
       </c>
       <c r="R8" t="n">
-        <v>7232864</v>
+        <v>7232818</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>125830904</v>
       </c>
       <c r="B9" t="n">
-        <v>77917</v>
+        <v>77921</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125830887</v>
+        <v>125830899</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>92522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>754137</v>
+        <v>754209</v>
       </c>
       <c r="R10" t="n">
-        <v>7232854</v>
+        <v>7232812</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125830899</v>
+        <v>125830887</v>
       </c>
       <c r="B11" t="n">
-        <v>92518</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>754209</v>
+        <v>754137</v>
       </c>
       <c r="R11" t="n">
-        <v>7232812</v>
+        <v>7232854</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>125830902</v>
       </c>
       <c r="B12" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125830906</v>
       </c>
       <c r="B13" t="n">
-        <v>78374</v>
+        <v>78378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125830894</v>
+        <v>125830900</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>92522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>754346</v>
+        <v>754156</v>
       </c>
       <c r="R14" t="n">
-        <v>7232860</v>
+        <v>7232842</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125830900</v>
+        <v>125830894</v>
       </c>
       <c r="B15" t="n">
-        <v>92518</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754156</v>
+        <v>754346</v>
       </c>
       <c r="R15" t="n">
-        <v>7232842</v>
+        <v>7232860</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,7 +2138,7 @@
         <v>125830895</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>125830881</v>
       </c>
       <c r="B19" t="n">
-        <v>92710</v>
+        <v>92714</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125830888</v>
+        <v>125830896</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754263</v>
+        <v>754778</v>
       </c>
       <c r="R20" t="n">
-        <v>7232863</v>
+        <v>7232929</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125830889</v>
+        <v>125830888</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754295</v>
+        <v>754263</v>
       </c>
       <c r="R21" t="n">
-        <v>7232868</v>
+        <v>7232863</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125830896</v>
+        <v>125830889</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754778</v>
+        <v>754295</v>
       </c>
       <c r="R22" t="n">
-        <v>7232929</v>
+        <v>7232868</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,7 +2729,7 @@
         <v>125830892</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>125830890</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125830879</v>
+        <v>125830898</v>
       </c>
       <c r="B25" t="n">
-        <v>97218</v>
+        <v>92522</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754396</v>
+        <v>754233</v>
       </c>
       <c r="R25" t="n">
-        <v>7232865</v>
+        <v>7232850</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,32 +3017,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125830898</v>
+        <v>125830893</v>
       </c>
       <c r="B26" t="n">
-        <v>92518</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>754233</v>
+        <v>754361</v>
       </c>
       <c r="R26" t="n">
-        <v>7232850</v>
+        <v>7232867</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,32 +3114,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125830893</v>
+        <v>125830879</v>
       </c>
       <c r="B27" t="n">
-        <v>78968</v>
+        <v>97222</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>754361</v>
+        <v>754396</v>
       </c>
       <c r="R27" t="n">
-        <v>7232867</v>
+        <v>7232865</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,7 +3214,7 @@
         <v>125830878</v>
       </c>
       <c r="B28" t="n">
-        <v>97218</v>
+        <v>97222</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>125830873</v>
       </c>
       <c r="B29" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125830880</v>
+        <v>125830903</v>
       </c>
       <c r="B3" t="n">
-        <v>97222</v>
+        <v>92522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754257</v>
+        <v>754728</v>
       </c>
       <c r="R3" t="n">
-        <v>7232865</v>
+        <v>7232863</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125830903</v>
+        <v>125830880</v>
       </c>
       <c r="B4" t="n">
-        <v>92522</v>
+        <v>97223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754728</v>
+        <v>754257</v>
       </c>
       <c r="R4" t="n">
-        <v>7232863</v>
+        <v>7232865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125830902</v>
+        <v>125830906</v>
       </c>
       <c r="B12" t="n">
-        <v>92522</v>
+        <v>78378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>754793</v>
+        <v>754373</v>
       </c>
       <c r="R12" t="n">
-        <v>7232966</v>
+        <v>7232867</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125830906</v>
+        <v>125830902</v>
       </c>
       <c r="B13" t="n">
-        <v>78378</v>
+        <v>92522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>754373</v>
+        <v>754793</v>
       </c>
       <c r="R13" t="n">
-        <v>7232867</v>
+        <v>7232966</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125830900</v>
+        <v>125830894</v>
       </c>
       <c r="B14" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>754156</v>
+        <v>754346</v>
       </c>
       <c r="R14" t="n">
-        <v>7232842</v>
+        <v>7232860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125830894</v>
+        <v>125830900</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754346</v>
+        <v>754156</v>
       </c>
       <c r="R15" t="n">
-        <v>7232860</v>
+        <v>7232842</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125830881</v>
+        <v>125830896</v>
       </c>
       <c r="B19" t="n">
-        <v>92714</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754471</v>
+        <v>754778</v>
       </c>
       <c r="R19" t="n">
-        <v>7232852</v>
+        <v>7232929</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2435,7 +2435,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125830896</v>
+        <v>125830889</v>
       </c>
       <c r="B20" t="n">
         <v>78972</v>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754778</v>
+        <v>754295</v>
       </c>
       <c r="R20" t="n">
-        <v>7232929</v>
+        <v>7232868</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125830888</v>
+        <v>125830881</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>92714</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2543,21 +2543,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754263</v>
+        <v>754471</v>
       </c>
       <c r="R21" t="n">
-        <v>7232863</v>
+        <v>7232852</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125830889</v>
+        <v>125830888</v>
       </c>
       <c r="B22" t="n">
         <v>78972</v>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754295</v>
+        <v>754263</v>
       </c>
       <c r="R22" t="n">
-        <v>7232868</v>
+        <v>7232863</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2920,32 +2920,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125830898</v>
+        <v>125830893</v>
       </c>
       <c r="B25" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754233</v>
+        <v>754361</v>
       </c>
       <c r="R25" t="n">
-        <v>7232850</v>
+        <v>7232867</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,32 +3017,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125830893</v>
+        <v>125830879</v>
       </c>
       <c r="B26" t="n">
-        <v>78972</v>
+        <v>97223</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>754361</v>
+        <v>754396</v>
       </c>
       <c r="R26" t="n">
-        <v>7232867</v>
+        <v>7232865</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125830879</v>
+        <v>125830898</v>
       </c>
       <c r="B27" t="n">
-        <v>97222</v>
+        <v>92522</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>754396</v>
+        <v>754233</v>
       </c>
       <c r="R27" t="n">
-        <v>7232865</v>
+        <v>7232850</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,7 +3214,7 @@
         <v>125830878</v>
       </c>
       <c r="B28" t="n">
-        <v>97222</v>
+        <v>97223</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125830901</v>
+        <v>125830876</v>
       </c>
       <c r="B7" t="n">
-        <v>92522</v>
+        <v>57811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754244</v>
+        <v>754171</v>
       </c>
       <c r="R7" t="n">
-        <v>7232864</v>
+        <v>7232818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125830876</v>
+        <v>125830901</v>
       </c>
       <c r="B8" t="n">
-        <v>57811</v>
+        <v>92522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754171</v>
+        <v>754244</v>
       </c>
       <c r="R8" t="n">
-        <v>7232818</v>
+        <v>7232864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125830899</v>
+        <v>125830887</v>
       </c>
       <c r="B10" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>754209</v>
+        <v>754137</v>
       </c>
       <c r="R10" t="n">
-        <v>7232812</v>
+        <v>7232854</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125830887</v>
+        <v>125830899</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>754137</v>
+        <v>754209</v>
       </c>
       <c r="R11" t="n">
-        <v>7232854</v>
+        <v>7232812</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125830906</v>
+        <v>125830902</v>
       </c>
       <c r="B12" t="n">
-        <v>78378</v>
+        <v>92522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>754373</v>
+        <v>754793</v>
       </c>
       <c r="R12" t="n">
-        <v>7232867</v>
+        <v>7232966</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125830902</v>
+        <v>125830906</v>
       </c>
       <c r="B13" t="n">
-        <v>92522</v>
+        <v>78378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>754793</v>
+        <v>754373</v>
       </c>
       <c r="R13" t="n">
-        <v>7232966</v>
+        <v>7232867</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125830894</v>
+        <v>125830900</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>754346</v>
+        <v>754156</v>
       </c>
       <c r="R14" t="n">
-        <v>7232860</v>
+        <v>7232842</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125830900</v>
+        <v>125830894</v>
       </c>
       <c r="B15" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754156</v>
+        <v>754346</v>
       </c>
       <c r="R15" t="n">
-        <v>7232842</v>
+        <v>7232860</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,45 +2135,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125830895</v>
+        <v>125830875</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>56843</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754569</v>
+        <v>754186</v>
       </c>
       <c r="R17" t="n">
-        <v>7232779</v>
+        <v>7232895</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2206,6 +2210,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,49 +2241,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125830875</v>
+        <v>125830895</v>
       </c>
       <c r="B18" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754186</v>
+        <v>754569</v>
       </c>
       <c r="R18" t="n">
-        <v>7232895</v>
+        <v>7232779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2307,11 +2312,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125830887</v>
+        <v>125830899</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>754137</v>
+        <v>754209</v>
       </c>
       <c r="R10" t="n">
-        <v>7232854</v>
+        <v>7232812</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125830899</v>
+        <v>125830887</v>
       </c>
       <c r="B11" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>754209</v>
+        <v>754137</v>
       </c>
       <c r="R11" t="n">
-        <v>7232812</v>
+        <v>7232854</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125830900</v>
+        <v>125830894</v>
       </c>
       <c r="B14" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>754156</v>
+        <v>754346</v>
       </c>
       <c r="R14" t="n">
-        <v>7232842</v>
+        <v>7232860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125830894</v>
+        <v>125830900</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754346</v>
+        <v>754156</v>
       </c>
       <c r="R15" t="n">
-        <v>7232860</v>
+        <v>7232842</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125830874</v>
+        <v>125830895</v>
       </c>
       <c r="B16" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754163</v>
+        <v>754569</v>
       </c>
       <c r="R16" t="n">
-        <v>7232894</v>
+        <v>7232779</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2104,11 +2104,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2135,49 +2130,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125830875</v>
+        <v>125830896</v>
       </c>
       <c r="B17" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754186</v>
+        <v>754778</v>
       </c>
       <c r="R17" t="n">
-        <v>7232895</v>
+        <v>7232929</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,11 +2201,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2241,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125830895</v>
+        <v>125830889</v>
       </c>
       <c r="B18" t="n">
         <v>78972</v>
@@ -2276,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754569</v>
+        <v>754295</v>
       </c>
       <c r="R18" t="n">
-        <v>7232779</v>
+        <v>7232868</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2338,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125830896</v>
+        <v>125830881</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>92714</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754778</v>
+        <v>754471</v>
       </c>
       <c r="R19" t="n">
-        <v>7232929</v>
+        <v>7232852</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2435,7 +2421,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125830889</v>
+        <v>125830888</v>
       </c>
       <c r="B20" t="n">
         <v>78972</v>
@@ -2470,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754295</v>
+        <v>754263</v>
       </c>
       <c r="R20" t="n">
-        <v>7232868</v>
+        <v>7232863</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125830881</v>
+        <v>125830892</v>
       </c>
       <c r="B21" t="n">
-        <v>92714</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2543,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2567,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754471</v>
+        <v>754336</v>
       </c>
       <c r="R21" t="n">
-        <v>7232852</v>
+        <v>7232856</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2629,7 +2615,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125830888</v>
+        <v>125830890</v>
       </c>
       <c r="B22" t="n">
         <v>78972</v>
@@ -2664,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754263</v>
+        <v>754314</v>
       </c>
       <c r="R22" t="n">
-        <v>7232863</v>
+        <v>7232874</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,7 +2712,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125830892</v>
+        <v>125830893</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2761,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>754336</v>
+        <v>754361</v>
       </c>
       <c r="R23" t="n">
-        <v>7232856</v>
+        <v>7232867</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2823,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125830890</v>
+        <v>125830898</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754314</v>
+        <v>754233</v>
       </c>
       <c r="R24" t="n">
-        <v>7232874</v>
+        <v>7232850</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2920,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125830893</v>
+        <v>125830879</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>97223</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754361</v>
+        <v>754396</v>
       </c>
       <c r="R25" t="n">
-        <v>7232867</v>
+        <v>7232865</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,7 +3003,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125830879</v>
+        <v>125830878</v>
       </c>
       <c r="B26" t="n">
         <v>97223</v>
@@ -3052,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>754396</v>
+        <v>754593</v>
       </c>
       <c r="R26" t="n">
-        <v>7232865</v>
+        <v>7232914</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125830898</v>
+        <v>125830873</v>
       </c>
       <c r="B27" t="n">
-        <v>92522</v>
+        <v>79561</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>754233</v>
+        <v>754163</v>
       </c>
       <c r="R27" t="n">
-        <v>7232850</v>
+        <v>7232822</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3193,6 +3179,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3208,201 +3195,6 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>125830878</v>
-      </c>
-      <c r="B28" t="n">
-        <v>97223</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Snörsmyran, Vb</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>754593</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7232914</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Jörn</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>125830873</v>
-      </c>
-      <c r="B29" t="n">
-        <v>79561</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Snörsmyran, Vb</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>754163</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7232822</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Jörn</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830883</v>
       </c>
       <c r="B2" t="n">
-        <v>91228</v>
+        <v>91230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125830903</v>
       </c>
       <c r="B3" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125830880</v>
       </c>
       <c r="B4" t="n">
-        <v>97223</v>
+        <v>97225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125830877</v>
       </c>
       <c r="B5" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125830891</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125830876</v>
       </c>
       <c r="B7" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125830901</v>
       </c>
       <c r="B8" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125830904</v>
       </c>
       <c r="B9" t="n">
-        <v>77921</v>
+        <v>77922</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125830899</v>
       </c>
       <c r="B10" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125830887</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125830902</v>
       </c>
       <c r="B12" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125830906</v>
       </c>
       <c r="B13" t="n">
-        <v>78378</v>
+        <v>78379</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>125830894</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>125830900</v>
       </c>
       <c r="B15" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>125830895</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125830896</v>
+        <v>125830881</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>92716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754778</v>
+        <v>754471</v>
       </c>
       <c r="R17" t="n">
-        <v>7232929</v>
+        <v>7232852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2230,7 +2230,7 @@
         <v>125830889</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125830881</v>
+        <v>125830896</v>
       </c>
       <c r="B19" t="n">
-        <v>92714</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754471</v>
+        <v>754778</v>
       </c>
       <c r="R19" t="n">
-        <v>7232852</v>
+        <v>7232929</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
         <v>125830888</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>125830892</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>125830890</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>125830893</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125830898</v>
+        <v>125830879</v>
       </c>
       <c r="B24" t="n">
-        <v>92522</v>
+        <v>97225</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754233</v>
+        <v>754396</v>
       </c>
       <c r="R24" t="n">
-        <v>7232850</v>
+        <v>7232865</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125830879</v>
+        <v>125830898</v>
       </c>
       <c r="B25" t="n">
-        <v>97223</v>
+        <v>92524</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754396</v>
+        <v>754233</v>
       </c>
       <c r="R25" t="n">
-        <v>7232865</v>
+        <v>7232850</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3006,7 +3006,7 @@
         <v>125830878</v>
       </c>
       <c r="B26" t="n">
-        <v>97223</v>
+        <v>97225</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>125830873</v>
       </c>
       <c r="B27" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830883</v>
       </c>
       <c r="B2" t="n">
-        <v>91230</v>
+        <v>91232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125830903</v>
       </c>
       <c r="B3" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125830880</v>
       </c>
       <c r="B4" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125830901</v>
       </c>
       <c r="B8" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125830899</v>
       </c>
       <c r="B10" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125830902</v>
       </c>
       <c r="B12" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125830894</v>
+        <v>125830900</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>92526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>754346</v>
+        <v>754156</v>
       </c>
       <c r="R14" t="n">
-        <v>7232860</v>
+        <v>7232842</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125830900</v>
+        <v>125830894</v>
       </c>
       <c r="B15" t="n">
-        <v>92524</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754156</v>
+        <v>754346</v>
       </c>
       <c r="R15" t="n">
-        <v>7232842</v>
+        <v>7232860</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>125830881</v>
       </c>
       <c r="B17" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125830889</v>
+        <v>125830896</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754295</v>
+        <v>754778</v>
       </c>
       <c r="R18" t="n">
-        <v>7232868</v>
+        <v>7232929</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125830896</v>
+        <v>125830889</v>
       </c>
       <c r="B19" t="n">
         <v>78973</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754778</v>
+        <v>754295</v>
       </c>
       <c r="R19" t="n">
-        <v>7232929</v>
+        <v>7232868</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125830893</v>
+        <v>125830898</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>92526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>754361</v>
+        <v>754233</v>
       </c>
       <c r="R23" t="n">
-        <v>7232867</v>
+        <v>7232850</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125830879</v>
+        <v>125830893</v>
       </c>
       <c r="B24" t="n">
-        <v>97225</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754396</v>
+        <v>754361</v>
       </c>
       <c r="R24" t="n">
-        <v>7232865</v>
+        <v>7232867</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125830898</v>
+        <v>125830879</v>
       </c>
       <c r="B25" t="n">
-        <v>92524</v>
+        <v>97227</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754233</v>
+        <v>754396</v>
       </c>
       <c r="R25" t="n">
-        <v>7232850</v>
+        <v>7232865</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3006,7 +3006,7 @@
         <v>125830878</v>
       </c>
       <c r="B26" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125830876</v>
+        <v>125830901</v>
       </c>
       <c r="B7" t="n">
-        <v>57812</v>
+        <v>92526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754171</v>
+        <v>754244</v>
       </c>
       <c r="R7" t="n">
-        <v>7232818</v>
+        <v>7232864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125830901</v>
+        <v>125830876</v>
       </c>
       <c r="B8" t="n">
-        <v>92526</v>
+        <v>57812</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754244</v>
+        <v>754171</v>
       </c>
       <c r="R8" t="n">
-        <v>7232864</v>
+        <v>7232818</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830883</v>
       </c>
       <c r="B2" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125830903</v>
+        <v>125830880</v>
       </c>
       <c r="B3" t="n">
-        <v>92526</v>
+        <v>97229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754728</v>
+        <v>754257</v>
       </c>
       <c r="R3" t="n">
-        <v>7232863</v>
+        <v>7232865</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125830880</v>
+        <v>125830903</v>
       </c>
       <c r="B4" t="n">
-        <v>97227</v>
+        <v>92528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754257</v>
+        <v>754728</v>
       </c>
       <c r="R4" t="n">
-        <v>7232865</v>
+        <v>7232863</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>125830901</v>
       </c>
       <c r="B7" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125830899</v>
+        <v>125830887</v>
       </c>
       <c r="B10" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>754209</v>
+        <v>754137</v>
       </c>
       <c r="R10" t="n">
-        <v>7232812</v>
+        <v>7232854</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125830887</v>
+        <v>125830899</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>754137</v>
+        <v>754209</v>
       </c>
       <c r="R11" t="n">
-        <v>7232854</v>
+        <v>7232812</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125830902</v>
+        <v>125830906</v>
       </c>
       <c r="B12" t="n">
-        <v>92526</v>
+        <v>78379</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>754793</v>
+        <v>754373</v>
       </c>
       <c r="R12" t="n">
-        <v>7232966</v>
+        <v>7232867</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125830906</v>
+        <v>125830902</v>
       </c>
       <c r="B13" t="n">
-        <v>78379</v>
+        <v>92528</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>754373</v>
+        <v>754793</v>
       </c>
       <c r="R13" t="n">
-        <v>7232867</v>
+        <v>7232966</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125830900</v>
+        <v>125830894</v>
       </c>
       <c r="B14" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>754156</v>
+        <v>754346</v>
       </c>
       <c r="R14" t="n">
-        <v>7232842</v>
+        <v>7232860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125830894</v>
+        <v>125830900</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754346</v>
+        <v>754156</v>
       </c>
       <c r="R15" t="n">
-        <v>7232860</v>
+        <v>7232842</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125830881</v>
+        <v>125830888</v>
       </c>
       <c r="B17" t="n">
-        <v>92718</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754471</v>
+        <v>754263</v>
       </c>
       <c r="R17" t="n">
-        <v>7232852</v>
+        <v>7232863</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125830896</v>
+        <v>125830889</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754778</v>
+        <v>754295</v>
       </c>
       <c r="R18" t="n">
-        <v>7232929</v>
+        <v>7232868</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125830889</v>
+        <v>125830896</v>
       </c>
       <c r="B19" t="n">
         <v>78973</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754295</v>
+        <v>754778</v>
       </c>
       <c r="R19" t="n">
-        <v>7232868</v>
+        <v>7232929</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125830888</v>
+        <v>125830881</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>92720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754263</v>
+        <v>754471</v>
       </c>
       <c r="R20" t="n">
-        <v>7232863</v>
+        <v>7232852</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125830898</v>
+        <v>125830893</v>
       </c>
       <c r="B23" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>754233</v>
+        <v>754361</v>
       </c>
       <c r="R23" t="n">
-        <v>7232850</v>
+        <v>7232867</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125830893</v>
+        <v>125830898</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754361</v>
+        <v>754233</v>
       </c>
       <c r="R24" t="n">
-        <v>7232867</v>
+        <v>7232850</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2909,7 +2909,7 @@
         <v>125830879</v>
       </c>
       <c r="B25" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>125830878</v>
       </c>
       <c r="B26" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125830894</v>
+        <v>125830900</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>754346</v>
+        <v>754156</v>
       </c>
       <c r="R14" t="n">
-        <v>7232860</v>
+        <v>7232842</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125830900</v>
+        <v>125830894</v>
       </c>
       <c r="B15" t="n">
-        <v>92528</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754156</v>
+        <v>754346</v>
       </c>
       <c r="R15" t="n">
-        <v>7232842</v>
+        <v>7232860</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830883</v>
       </c>
       <c r="B2" t="n">
-        <v>91234</v>
+        <v>91238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125830880</v>
+        <v>125830903</v>
       </c>
       <c r="B3" t="n">
-        <v>97229</v>
+        <v>92532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754257</v>
+        <v>754728</v>
       </c>
       <c r="R3" t="n">
-        <v>7232865</v>
+        <v>7232863</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125830903</v>
+        <v>125830880</v>
       </c>
       <c r="B4" t="n">
-        <v>92528</v>
+        <v>97233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754728</v>
+        <v>754257</v>
       </c>
       <c r="R4" t="n">
-        <v>7232863</v>
+        <v>7232865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>125830877</v>
       </c>
       <c r="B5" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125830891</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125830901</v>
       </c>
       <c r="B7" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125830876</v>
       </c>
       <c r="B8" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125830904</v>
       </c>
       <c r="B9" t="n">
-        <v>77922</v>
+        <v>77926</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125830887</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125830899</v>
       </c>
       <c r="B11" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125830906</v>
+        <v>125830902</v>
       </c>
       <c r="B12" t="n">
-        <v>78379</v>
+        <v>92532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>754373</v>
+        <v>754793</v>
       </c>
       <c r="R12" t="n">
-        <v>7232867</v>
+        <v>7232966</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125830902</v>
+        <v>125830906</v>
       </c>
       <c r="B13" t="n">
-        <v>92528</v>
+        <v>78383</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>754793</v>
+        <v>754373</v>
       </c>
       <c r="R13" t="n">
-        <v>7232966</v>
+        <v>7232867</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
         <v>125830900</v>
       </c>
       <c r="B14" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>125830894</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>125830895</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125830888</v>
+        <v>125830896</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754263</v>
+        <v>754778</v>
       </c>
       <c r="R17" t="n">
-        <v>7232863</v>
+        <v>7232929</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2230,7 +2230,7 @@
         <v>125830889</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125830896</v>
+        <v>125830888</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754778</v>
+        <v>754263</v>
       </c>
       <c r="R19" t="n">
-        <v>7232929</v>
+        <v>7232863</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
         <v>125830881</v>
       </c>
       <c r="B20" t="n">
-        <v>92720</v>
+        <v>92724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>125830892</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>125830890</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125830893</v>
+        <v>125830898</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>92532</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>754361</v>
+        <v>754233</v>
       </c>
       <c r="R23" t="n">
-        <v>7232867</v>
+        <v>7232850</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125830898</v>
+        <v>125830893</v>
       </c>
       <c r="B24" t="n">
-        <v>92528</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754233</v>
+        <v>754361</v>
       </c>
       <c r="R24" t="n">
-        <v>7232850</v>
+        <v>7232867</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2909,7 +2909,7 @@
         <v>125830879</v>
       </c>
       <c r="B25" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>125830878</v>
       </c>
       <c r="B26" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>125830873</v>
       </c>
       <c r="B27" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125830887</v>
+        <v>125830899</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>754137</v>
+        <v>754209</v>
       </c>
       <c r="R10" t="n">
-        <v>7232854</v>
+        <v>7232812</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125830899</v>
+        <v>125830887</v>
       </c>
       <c r="B11" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>754209</v>
+        <v>754137</v>
       </c>
       <c r="R11" t="n">
-        <v>7232812</v>
+        <v>7232854</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125830880</v>
       </c>
       <c r="B4" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125830901</v>
+        <v>125830876</v>
       </c>
       <c r="B7" t="n">
-        <v>92532</v>
+        <v>57816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754244</v>
+        <v>754171</v>
       </c>
       <c r="R7" t="n">
-        <v>7232864</v>
+        <v>7232818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125830876</v>
+        <v>125830901</v>
       </c>
       <c r="B8" t="n">
-        <v>57816</v>
+        <v>92532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754171</v>
+        <v>754244</v>
       </c>
       <c r="R8" t="n">
-        <v>7232818</v>
+        <v>7232864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125830899</v>
+        <v>125830887</v>
       </c>
       <c r="B10" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>754209</v>
+        <v>754137</v>
       </c>
       <c r="R10" t="n">
-        <v>7232812</v>
+        <v>7232854</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125830887</v>
+        <v>125830899</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>754137</v>
+        <v>754209</v>
       </c>
       <c r="R11" t="n">
-        <v>7232854</v>
+        <v>7232812</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125830902</v>
+        <v>125830906</v>
       </c>
       <c r="B12" t="n">
-        <v>92532</v>
+        <v>78383</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>754793</v>
+        <v>754373</v>
       </c>
       <c r="R12" t="n">
-        <v>7232966</v>
+        <v>7232867</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125830906</v>
+        <v>125830902</v>
       </c>
       <c r="B13" t="n">
-        <v>78383</v>
+        <v>92532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>754373</v>
+        <v>754793</v>
       </c>
       <c r="R13" t="n">
-        <v>7232867</v>
+        <v>7232966</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125830900</v>
+        <v>125830894</v>
       </c>
       <c r="B14" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>754156</v>
+        <v>754346</v>
       </c>
       <c r="R14" t="n">
-        <v>7232842</v>
+        <v>7232860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125830894</v>
+        <v>125830900</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754346</v>
+        <v>754156</v>
       </c>
       <c r="R15" t="n">
-        <v>7232860</v>
+        <v>7232842</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125830896</v>
+        <v>125830881</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>92724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754778</v>
+        <v>754471</v>
       </c>
       <c r="R17" t="n">
-        <v>7232929</v>
+        <v>7232852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125830889</v>
+        <v>125830888</v>
       </c>
       <c r="B18" t="n">
         <v>78977</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754295</v>
+        <v>754263</v>
       </c>
       <c r="R18" t="n">
-        <v>7232868</v>
+        <v>7232863</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125830888</v>
+        <v>125830889</v>
       </c>
       <c r="B19" t="n">
         <v>78977</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754263</v>
+        <v>754295</v>
       </c>
       <c r="R19" t="n">
-        <v>7232863</v>
+        <v>7232868</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125830881</v>
+        <v>125830896</v>
       </c>
       <c r="B20" t="n">
-        <v>92724</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754471</v>
+        <v>754778</v>
       </c>
       <c r="R20" t="n">
-        <v>7232852</v>
+        <v>7232929</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125830893</v>
+        <v>125830879</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>97236</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754361</v>
+        <v>754396</v>
       </c>
       <c r="R24" t="n">
-        <v>7232867</v>
+        <v>7232865</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125830879</v>
+        <v>125830893</v>
       </c>
       <c r="B25" t="n">
-        <v>97233</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754396</v>
+        <v>754361</v>
       </c>
       <c r="R25" t="n">
-        <v>7232865</v>
+        <v>7232867</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3006,7 +3006,7 @@
         <v>125830878</v>
       </c>
       <c r="B26" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125830881</v>
+        <v>125830888</v>
       </c>
       <c r="B17" t="n">
-        <v>92724</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754471</v>
+        <v>754263</v>
       </c>
       <c r="R17" t="n">
-        <v>7232852</v>
+        <v>7232863</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125830888</v>
+        <v>125830889</v>
       </c>
       <c r="B18" t="n">
         <v>78977</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754263</v>
+        <v>754295</v>
       </c>
       <c r="R18" t="n">
-        <v>7232863</v>
+        <v>7232868</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125830889</v>
+        <v>125830896</v>
       </c>
       <c r="B19" t="n">
         <v>78977</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754295</v>
+        <v>754778</v>
       </c>
       <c r="R19" t="n">
-        <v>7232868</v>
+        <v>7232929</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125830896</v>
+        <v>125830881</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>92724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754778</v>
+        <v>754471</v>
       </c>
       <c r="R20" t="n">
-        <v>7232929</v>
+        <v>7232852</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125830903</v>
+        <v>125830880</v>
       </c>
       <c r="B3" t="n">
-        <v>92532</v>
+        <v>97236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754728</v>
+        <v>754257</v>
       </c>
       <c r="R3" t="n">
-        <v>7232863</v>
+        <v>7232865</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125830880</v>
+        <v>125830903</v>
       </c>
       <c r="B4" t="n">
-        <v>97236</v>
+        <v>92532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754257</v>
+        <v>754728</v>
       </c>
       <c r="R4" t="n">
-        <v>7232865</v>
+        <v>7232863</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125830876</v>
+        <v>125830901</v>
       </c>
       <c r="B7" t="n">
-        <v>57816</v>
+        <v>92532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754171</v>
+        <v>754244</v>
       </c>
       <c r="R7" t="n">
-        <v>7232818</v>
+        <v>7232864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125830901</v>
+        <v>125830876</v>
       </c>
       <c r="B8" t="n">
-        <v>92532</v>
+        <v>57816</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754244</v>
+        <v>754171</v>
       </c>
       <c r="R8" t="n">
-        <v>7232864</v>
+        <v>7232818</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125830894</v>
+        <v>125830900</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>754346</v>
+        <v>754156</v>
       </c>
       <c r="R14" t="n">
-        <v>7232860</v>
+        <v>7232842</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125830900</v>
+        <v>125830894</v>
       </c>
       <c r="B15" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754156</v>
+        <v>754346</v>
       </c>
       <c r="R15" t="n">
-        <v>7232842</v>
+        <v>7232860</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125830888</v>
+        <v>125830881</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>92724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754263</v>
+        <v>754471</v>
       </c>
       <c r="R17" t="n">
-        <v>7232863</v>
+        <v>7232852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125830889</v>
+        <v>125830888</v>
       </c>
       <c r="B18" t="n">
         <v>78977</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754295</v>
+        <v>754263</v>
       </c>
       <c r="R18" t="n">
-        <v>7232868</v>
+        <v>7232863</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125830896</v>
+        <v>125830889</v>
       </c>
       <c r="B19" t="n">
         <v>78977</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754778</v>
+        <v>754295</v>
       </c>
       <c r="R19" t="n">
-        <v>7232929</v>
+        <v>7232868</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125830881</v>
+        <v>125830896</v>
       </c>
       <c r="B20" t="n">
-        <v>92724</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754471</v>
+        <v>754778</v>
       </c>
       <c r="R20" t="n">
-        <v>7232852</v>
+        <v>7232929</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125830879</v>
+        <v>125830893</v>
       </c>
       <c r="B24" t="n">
-        <v>97236</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754396</v>
+        <v>754361</v>
       </c>
       <c r="R24" t="n">
-        <v>7232865</v>
+        <v>7232867</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125830893</v>
+        <v>125830879</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>97236</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754361</v>
+        <v>754396</v>
       </c>
       <c r="R25" t="n">
-        <v>7232867</v>
+        <v>7232865</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830883</v>
       </c>
       <c r="B2" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125830880</v>
+        <v>125830903</v>
       </c>
       <c r="B3" t="n">
-        <v>97236</v>
+        <v>92535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754257</v>
+        <v>754728</v>
       </c>
       <c r="R3" t="n">
-        <v>7232865</v>
+        <v>7232863</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125830903</v>
+        <v>125830880</v>
       </c>
       <c r="B4" t="n">
-        <v>92532</v>
+        <v>97245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754728</v>
+        <v>754257</v>
       </c>
       <c r="R4" t="n">
-        <v>7232863</v>
+        <v>7232865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>125830877</v>
       </c>
       <c r="B5" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125830891</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125830901</v>
       </c>
       <c r="B7" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125830876</v>
       </c>
       <c r="B8" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125830904</v>
       </c>
       <c r="B9" t="n">
-        <v>77926</v>
+        <v>77929</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125830887</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125830899</v>
       </c>
       <c r="B11" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125830906</v>
       </c>
       <c r="B12" t="n">
-        <v>78383</v>
+        <v>78386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125830902</v>
       </c>
       <c r="B13" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125830900</v>
+        <v>125830894</v>
       </c>
       <c r="B14" t="n">
-        <v>92532</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>754156</v>
+        <v>754346</v>
       </c>
       <c r="R14" t="n">
-        <v>7232842</v>
+        <v>7232860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125830894</v>
+        <v>125830900</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>92535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754346</v>
+        <v>754156</v>
       </c>
       <c r="R15" t="n">
-        <v>7232860</v>
+        <v>7232842</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>125830895</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>125830881</v>
       </c>
       <c r="B17" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>125830888</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>125830889</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>125830896</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>125830892</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>125830890</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>125830898</v>
       </c>
       <c r="B23" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>125830893</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>125830879</v>
       </c>
       <c r="B25" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>125830878</v>
       </c>
       <c r="B26" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>125830873</v>
       </c>
       <c r="B27" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125830906</v>
+        <v>125830902</v>
       </c>
       <c r="B12" t="n">
-        <v>78386</v>
+        <v>92535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>754373</v>
+        <v>754793</v>
       </c>
       <c r="R12" t="n">
-        <v>7232867</v>
+        <v>7232966</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125830902</v>
+        <v>125830906</v>
       </c>
       <c r="B13" t="n">
-        <v>92535</v>
+        <v>78386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>754793</v>
+        <v>754373</v>
       </c>
       <c r="R13" t="n">
-        <v>7232966</v>
+        <v>7232867</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830883</v>
       </c>
       <c r="B2" t="n">
-        <v>91241</v>
+        <v>91326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>125830903</v>
       </c>
       <c r="B3" t="n">
-        <v>92535</v>
+        <v>92620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>125830880</v>
       </c>
       <c r="B4" t="n">
-        <v>97245</v>
+        <v>97331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,14 +970,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>125830877</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,14 +1071,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>125830891</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,14 +1172,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>125830901</v>
       </c>
       <c r="B7" t="n">
-        <v>92535</v>
+        <v>92620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,14 +1273,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>125830876</v>
       </c>
       <c r="B8" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,14 +1374,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>125830904</v>
       </c>
       <c r="B9" t="n">
-        <v>77929</v>
+        <v>77996</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,14 +1475,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>125830887</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,14 +1576,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>125830899</v>
       </c>
       <c r="B11" t="n">
-        <v>92535</v>
+        <v>92620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,14 +1677,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>125830902</v>
       </c>
       <c r="B12" t="n">
-        <v>92535</v>
+        <v>92620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,14 +1778,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>125830906</v>
       </c>
       <c r="B13" t="n">
-        <v>78386</v>
+        <v>78424</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,14 +1879,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>125830894</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,14 +1980,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>125830900</v>
       </c>
       <c r="B15" t="n">
-        <v>92535</v>
+        <v>92620</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2029,14 +2081,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>125830895</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2126,14 +2182,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>125830881</v>
       </c>
       <c r="B17" t="n">
-        <v>92727</v>
+        <v>92813</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2223,14 +2283,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>125830888</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2320,14 +2384,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>125830889</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,14 +2485,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>125830896</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2514,14 +2586,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>125830892</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2611,14 +2687,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>125830890</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2708,14 +2788,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>125830898</v>
       </c>
       <c r="B23" t="n">
-        <v>92535</v>
+        <v>92620</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2805,14 +2889,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>125830893</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2902,14 +2990,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>125830879</v>
       </c>
       <c r="B25" t="n">
-        <v>97245</v>
+        <v>97331</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2999,14 +3091,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>125830878</v>
       </c>
       <c r="B26" t="n">
-        <v>97245</v>
+        <v>97331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3096,14 +3192,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>125830873</v>
       </c>
       <c r="B27" t="n">
-        <v>79569</v>
+        <v>79607</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3194,7 +3294,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830883</v>
       </c>
       <c r="B2" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>125830903</v>
       </c>
       <c r="B3" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125830880</v>
       </c>
       <c r="B4" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>125830877</v>
       </c>
       <c r="B5" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>125830891</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>125830901</v>
       </c>
       <c r="B7" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>125830876</v>
       </c>
       <c r="B8" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>125830904</v>
       </c>
       <c r="B9" t="n">
-        <v>77996</v>
+        <v>77998</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>125830887</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>125830899</v>
       </c>
       <c r="B11" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>125830902</v>
       </c>
       <c r="B12" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>125830906</v>
       </c>
       <c r="B13" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>125830894</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>125830900</v>
       </c>
       <c r="B15" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>125830895</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>125830881</v>
       </c>
       <c r="B17" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>125830888</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>125830889</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>125830896</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>125830892</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>125830890</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>125830898</v>
       </c>
       <c r="B23" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>125830893</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>125830879</v>
       </c>
       <c r="B25" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>125830878</v>
       </c>
       <c r="B26" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>125830873</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830883</v>
       </c>
       <c r="B2" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>125830903</v>
       </c>
       <c r="B3" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125830880</v>
       </c>
       <c r="B4" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>125830901</v>
       </c>
       <c r="B7" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>125830899</v>
       </c>
       <c r="B11" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>125830902</v>
       </c>
       <c r="B12" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>125830900</v>
       </c>
       <c r="B15" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>125830881</v>
       </c>
       <c r="B17" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>125830898</v>
       </c>
       <c r="B23" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>125830879</v>
       </c>
       <c r="B25" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>125830878</v>
       </c>
       <c r="B26" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830883</v>
       </c>
       <c r="B2" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>125830903</v>
       </c>
       <c r="B3" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125830880</v>
       </c>
       <c r="B4" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>125830877</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>125830891</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>125830901</v>
       </c>
       <c r="B7" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>125830876</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>125830904</v>
       </c>
       <c r="B9" t="n">
-        <v>77998</v>
+        <v>78001</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>125830887</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>125830899</v>
       </c>
       <c r="B11" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>125830902</v>
       </c>
       <c r="B12" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>125830906</v>
       </c>
       <c r="B13" t="n">
-        <v>78426</v>
+        <v>78429</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>125830894</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>125830900</v>
       </c>
       <c r="B15" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>125830895</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>125830881</v>
       </c>
       <c r="B17" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>125830888</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>125830889</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>125830896</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>125830892</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>125830890</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>125830898</v>
       </c>
       <c r="B23" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>125830893</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>125830879</v>
       </c>
       <c r="B25" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>125830878</v>
       </c>
       <c r="B26" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>125830873</v>
       </c>
       <c r="B27" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47887-2024 artfynd.xlsx
+++ b/artfynd/A 47887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830883</v>
       </c>
       <c r="B2" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>125830903</v>
       </c>
       <c r="B3" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125830880</v>
       </c>
       <c r="B4" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>125830877</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>125830891</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>125830901</v>
       </c>
       <c r="B7" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>125830876</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>125830904</v>
       </c>
       <c r="B9" t="n">
-        <v>78001</v>
+        <v>78007</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>125830887</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>125830899</v>
       </c>
       <c r="B11" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>125830902</v>
       </c>
       <c r="B12" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>125830906</v>
       </c>
       <c r="B13" t="n">
-        <v>78429</v>
+        <v>78435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>125830894</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>125830900</v>
       </c>
       <c r="B15" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>125830895</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>125830881</v>
       </c>
       <c r="B17" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>125830888</v>
       </c>
       <c r="B18" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>125830889</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>125830896</v>
       </c>
       <c r="B20" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>125830892</v>
       </c>
       <c r="B21" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>125830890</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>125830898</v>
       </c>
       <c r="B23" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>125830893</v>
       </c>
       <c r="B24" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>125830879</v>
       </c>
       <c r="B25" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>125830878</v>
       </c>
       <c r="B26" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>125830873</v>
       </c>
       <c r="B27" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
